--- a/DBs/nfl/Results/NFL_2024_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2024_Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\TracerProjects2\NFL_Elo\Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\tracersports-app\DBs\nfl\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{62BF1669-39D2-4736-9E10-673ADB9DD702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8324E01-B256-4674-B4D4-BD6668DCE20C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{86C9D044-819E-4134-B7A0-9B57B1FCB91D}"/>
   </bookViews>
@@ -130,12 +130,6 @@
     <t>DEN</t>
   </si>
   <si>
-    <t>SD</t>
-  </si>
-  <si>
-    <t>OAK</t>
-  </si>
-  <si>
     <t>DAL</t>
   </si>
   <si>
@@ -149,9 +143,6 @@
   </si>
   <si>
     <t>DET</t>
-  </si>
-  <si>
-    <t>STL</t>
   </si>
   <si>
     <t>SF</t>
@@ -176,6 +167,15 @@
   </si>
   <si>
     <t>N</t>
+  </si>
+  <si>
+    <t>LV</t>
+  </si>
+  <si>
+    <t>LAR</t>
+  </si>
+  <si>
+    <t>LAC</t>
   </si>
 </sst>
 </file>
@@ -1773,10 +1773,10 @@
         <v>11</v>
       </c>
       <c r="E24" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G24" t="s">
         <v>14</v>
@@ -1805,10 +1805,10 @@
         <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F25" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G25" t="s">
         <v>15</v>
@@ -1837,10 +1837,10 @@
         <v>11</v>
       </c>
       <c r="E26" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G26" t="s">
         <v>15</v>
@@ -1869,10 +1869,10 @@
         <v>11</v>
       </c>
       <c r="E27" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F27" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G27" t="s">
         <v>14</v>
@@ -1901,10 +1901,10 @@
         <v>11</v>
       </c>
       <c r="E28" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F28" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G28" t="s">
         <v>14</v>
@@ -1933,10 +1933,10 @@
         <v>11</v>
       </c>
       <c r="E29" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F29" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G29" t="s">
         <v>15</v>
@@ -1965,10 +1965,10 @@
         <v>11</v>
       </c>
       <c r="E30" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F30" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G30" t="s">
         <v>14</v>
@@ -1997,10 +1997,10 @@
         <v>11</v>
       </c>
       <c r="E31" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F31" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G31" t="s">
         <v>15</v>
@@ -2029,10 +2029,10 @@
         <v>11</v>
       </c>
       <c r="E32" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F32" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G32" t="s">
         <v>14</v>
@@ -2061,10 +2061,10 @@
         <v>11</v>
       </c>
       <c r="E33" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F33" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G33" t="s">
         <v>15</v>
@@ -2157,7 +2157,7 @@
         <v>11</v>
       </c>
       <c r="E36" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="F36" t="s">
         <v>23</v>
@@ -2192,7 +2192,7 @@
         <v>23</v>
       </c>
       <c r="F37" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G37" t="s">
         <v>14</v>
@@ -2221,7 +2221,7 @@
         <v>11</v>
       </c>
       <c r="E38" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F38" t="s">
         <v>31</v>
@@ -2256,7 +2256,7 @@
         <v>31</v>
       </c>
       <c r="F39" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G39" t="s">
         <v>14</v>
@@ -2352,7 +2352,7 @@
         <v>22</v>
       </c>
       <c r="F42" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G42" t="s">
         <v>15</v>
@@ -2381,7 +2381,7 @@
         <v>11</v>
       </c>
       <c r="E43" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F43" t="s">
         <v>22</v>
@@ -2413,10 +2413,10 @@
         <v>11</v>
       </c>
       <c r="E44" t="s">
+        <v>38</v>
+      </c>
+      <c r="F44" t="s">
         <v>40</v>
-      </c>
-      <c r="F44" t="s">
-        <v>42</v>
       </c>
       <c r="G44" t="s">
         <v>15</v>
@@ -2445,10 +2445,10 @@
         <v>11</v>
       </c>
       <c r="E45" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F45" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G45" t="s">
         <v>14</v>
@@ -2480,7 +2480,7 @@
         <v>32</v>
       </c>
       <c r="F46" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G46" t="s">
         <v>14</v>
@@ -2509,7 +2509,7 @@
         <v>11</v>
       </c>
       <c r="E47" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F47" t="s">
         <v>32</v>
@@ -2605,7 +2605,7 @@
         <v>11</v>
       </c>
       <c r="E50" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F50" t="s">
         <v>33</v>
@@ -2640,7 +2640,7 @@
         <v>33</v>
       </c>
       <c r="F51" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G51" t="s">
         <v>15</v>
@@ -2669,7 +2669,7 @@
         <v>11</v>
       </c>
       <c r="E52" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F52" t="s">
         <v>25</v>
@@ -2704,7 +2704,7 @@
         <v>25</v>
       </c>
       <c r="F53" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G53" t="s">
         <v>14</v>
@@ -2733,7 +2733,7 @@
         <v>11</v>
       </c>
       <c r="E54" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F54" t="s">
         <v>13</v>
@@ -2768,7 +2768,7 @@
         <v>13</v>
       </c>
       <c r="F55" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G55" t="s">
         <v>14</v>
@@ -2800,7 +2800,7 @@
         <v>21</v>
       </c>
       <c r="F56" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G56" t="s">
         <v>14</v>
@@ -2829,7 +2829,7 @@
         <v>11</v>
       </c>
       <c r="E57" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F57" t="s">
         <v>21</v>
@@ -3117,7 +3117,7 @@
         <v>11</v>
       </c>
       <c r="E66" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F66" t="s">
         <v>26</v>
@@ -3152,7 +3152,7 @@
         <v>26</v>
       </c>
       <c r="F67" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G67" t="s">
         <v>15</v>
@@ -3248,7 +3248,7 @@
         <v>33</v>
       </c>
       <c r="F70" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G70" t="s">
         <v>15</v>
@@ -3277,7 +3277,7 @@
         <v>11</v>
       </c>
       <c r="E71" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F71" t="s">
         <v>33</v>
@@ -3312,7 +3312,7 @@
         <v>35</v>
       </c>
       <c r="F72" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G72" t="s">
         <v>15</v>
@@ -3341,7 +3341,7 @@
         <v>11</v>
       </c>
       <c r="E73" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F73" t="s">
         <v>35</v>
@@ -3568,7 +3568,7 @@
         <v>18</v>
       </c>
       <c r="F80" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G80" t="s">
         <v>14</v>
@@ -3597,7 +3597,7 @@
         <v>11</v>
       </c>
       <c r="E81" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="F81" t="s">
         <v>18</v>
@@ -3632,7 +3632,7 @@
         <v>23</v>
       </c>
       <c r="F82" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G82" t="s">
         <v>15</v>
@@ -3661,7 +3661,7 @@
         <v>11</v>
       </c>
       <c r="E83" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F83" t="s">
         <v>23</v>
@@ -3757,7 +3757,7 @@
         <v>11</v>
       </c>
       <c r="E86" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F86" t="s">
         <v>21</v>
@@ -3792,7 +3792,7 @@
         <v>21</v>
       </c>
       <c r="F87" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G87" t="s">
         <v>14</v>
@@ -3824,7 +3824,7 @@
         <v>13</v>
       </c>
       <c r="F88" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G88" t="s">
         <v>15</v>
@@ -3853,7 +3853,7 @@
         <v>11</v>
       </c>
       <c r="E89" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F89" t="s">
         <v>13</v>
@@ -3885,10 +3885,10 @@
         <v>11</v>
       </c>
       <c r="E90" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F90" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G90" t="s">
         <v>14</v>
@@ -3917,10 +3917,10 @@
         <v>11</v>
       </c>
       <c r="E91" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F91" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G91" t="s">
         <v>15</v>
@@ -4077,7 +4077,7 @@
         <v>11</v>
       </c>
       <c r="E96" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F96" t="s">
         <v>27</v>
@@ -4112,7 +4112,7 @@
         <v>27</v>
       </c>
       <c r="F97" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G97" t="s">
         <v>14</v>
@@ -4141,7 +4141,7 @@
         <v>11</v>
       </c>
       <c r="E98" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F98" t="s">
         <v>33</v>
@@ -4176,7 +4176,7 @@
         <v>33</v>
       </c>
       <c r="F99" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G99" t="s">
         <v>14</v>
@@ -4336,7 +4336,7 @@
         <v>24</v>
       </c>
       <c r="F104" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G104" t="s">
         <v>14</v>
@@ -4365,7 +4365,7 @@
         <v>11</v>
       </c>
       <c r="E105" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F105" t="s">
         <v>24</v>
@@ -4464,7 +4464,7 @@
         <v>35</v>
       </c>
       <c r="F108" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G108" t="s">
         <v>15</v>
@@ -4493,7 +4493,7 @@
         <v>11</v>
       </c>
       <c r="E109" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F109" t="s">
         <v>35</v>
@@ -4653,7 +4653,7 @@
         <v>11</v>
       </c>
       <c r="E114" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F114" t="s">
         <v>16</v>
@@ -4688,7 +4688,7 @@
         <v>16</v>
       </c>
       <c r="F115" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G115" t="s">
         <v>15</v>
@@ -4717,7 +4717,7 @@
         <v>11</v>
       </c>
       <c r="E116" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F116" t="s">
         <v>21</v>
@@ -4752,7 +4752,7 @@
         <v>21</v>
       </c>
       <c r="F117" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G117" t="s">
         <v>14</v>
@@ -4781,7 +4781,7 @@
         <v>11</v>
       </c>
       <c r="E118" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F118" t="s">
         <v>26</v>
@@ -4816,7 +4816,7 @@
         <v>26</v>
       </c>
       <c r="F119" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G119" t="s">
         <v>15</v>
@@ -4845,10 +4845,10 @@
         <v>11</v>
       </c>
       <c r="E120" t="s">
+        <v>49</v>
+      </c>
+      <c r="F120" t="s">
         <v>37</v>
-      </c>
-      <c r="F120" t="s">
-        <v>39</v>
       </c>
       <c r="G120" t="s">
         <v>14</v>
@@ -4877,10 +4877,10 @@
         <v>11</v>
       </c>
       <c r="E121" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F121" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G121" t="s">
         <v>15</v>
@@ -4912,7 +4912,7 @@
         <v>12</v>
       </c>
       <c r="F122" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G122" t="s">
         <v>15</v>
@@ -4941,7 +4941,7 @@
         <v>11</v>
       </c>
       <c r="E123" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="F123" t="s">
         <v>12</v>
@@ -5101,7 +5101,7 @@
         <v>11</v>
       </c>
       <c r="E128" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F128" t="s">
         <v>34</v>
@@ -5136,7 +5136,7 @@
         <v>34</v>
       </c>
       <c r="F129" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G129" t="s">
         <v>15</v>
@@ -5168,7 +5168,7 @@
         <v>19</v>
       </c>
       <c r="F130" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G130" t="s">
         <v>14</v>
@@ -5197,7 +5197,7 @@
         <v>11</v>
       </c>
       <c r="E131" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F131" t="s">
         <v>19</v>
@@ -5232,7 +5232,7 @@
         <v>32</v>
       </c>
       <c r="F132" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G132" t="s">
         <v>14</v>
@@ -5261,7 +5261,7 @@
         <v>11</v>
       </c>
       <c r="E133" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F133" t="s">
         <v>32</v>
@@ -5485,10 +5485,10 @@
         <v>11</v>
       </c>
       <c r="E140" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F140" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G140" t="s">
         <v>14</v>
@@ -5517,10 +5517,10 @@
         <v>11</v>
       </c>
       <c r="E141" t="s">
+        <v>37</v>
+      </c>
+      <c r="F141" t="s">
         <v>39</v>
-      </c>
-      <c r="F141" t="s">
-        <v>41</v>
       </c>
       <c r="G141" t="s">
         <v>15</v>
@@ -5680,7 +5680,7 @@
         <v>21</v>
       </c>
       <c r="F146" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G146" t="s">
         <v>15</v>
@@ -5709,7 +5709,7 @@
         <v>11</v>
       </c>
       <c r="E147" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F147" t="s">
         <v>21</v>
@@ -5744,7 +5744,7 @@
         <v>35</v>
       </c>
       <c r="F148" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G148" t="s">
         <v>14</v>
@@ -5773,7 +5773,7 @@
         <v>11</v>
       </c>
       <c r="E149" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F149" t="s">
         <v>35</v>
@@ -5808,7 +5808,7 @@
         <v>17</v>
       </c>
       <c r="F150" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G150" t="s">
         <v>15</v>
@@ -5837,7 +5837,7 @@
         <v>11</v>
       </c>
       <c r="E151" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F151" t="s">
         <v>17</v>
@@ -5933,7 +5933,7 @@
         <v>11</v>
       </c>
       <c r="E154" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F154" t="s">
         <v>18</v>
@@ -5968,7 +5968,7 @@
         <v>18</v>
       </c>
       <c r="F155" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G155" t="s">
         <v>14</v>
@@ -6061,7 +6061,7 @@
         <v>11</v>
       </c>
       <c r="E158" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F158" t="s">
         <v>34</v>
@@ -6096,7 +6096,7 @@
         <v>34</v>
       </c>
       <c r="F159" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G159" t="s">
         <v>14</v>
@@ -6192,7 +6192,7 @@
         <v>16</v>
       </c>
       <c r="F162" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G162" t="s">
         <v>14</v>
@@ -6221,7 +6221,7 @@
         <v>11</v>
       </c>
       <c r="E163" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F163" t="s">
         <v>16</v>
@@ -6445,7 +6445,7 @@
         <v>11</v>
       </c>
       <c r="E170" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F170" t="s">
         <v>22</v>
@@ -6480,7 +6480,7 @@
         <v>22</v>
       </c>
       <c r="F171" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G171" t="s">
         <v>14</v>
@@ -6512,7 +6512,7 @@
         <v>13</v>
       </c>
       <c r="F172" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G172" t="s">
         <v>14</v>
@@ -6541,7 +6541,7 @@
         <v>11</v>
       </c>
       <c r="E173" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F173" t="s">
         <v>13</v>
@@ -6573,7 +6573,7 @@
         <v>11</v>
       </c>
       <c r="E174" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="F174" t="s">
         <v>35</v>
@@ -6608,7 +6608,7 @@
         <v>35</v>
       </c>
       <c r="F175" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G175" t="s">
         <v>14</v>
@@ -6640,7 +6640,7 @@
         <v>18</v>
       </c>
       <c r="F176" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G176" t="s">
         <v>15</v>
@@ -6669,7 +6669,7 @@
         <v>11</v>
       </c>
       <c r="E177" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F177" t="s">
         <v>18</v>
@@ -6765,10 +6765,10 @@
         <v>11</v>
       </c>
       <c r="E180" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F180" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G180" t="s">
         <v>15</v>
@@ -6797,10 +6797,10 @@
         <v>11</v>
       </c>
       <c r="E181" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F181" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G181" t="s">
         <v>14</v>
@@ -6896,7 +6896,7 @@
         <v>20</v>
       </c>
       <c r="F184" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G184" t="s">
         <v>15</v>
@@ -6925,7 +6925,7 @@
         <v>11</v>
       </c>
       <c r="E185" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F185" t="s">
         <v>20</v>
@@ -7085,7 +7085,7 @@
         <v>11</v>
       </c>
       <c r="E190" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F190" t="s">
         <v>32</v>
@@ -7120,7 +7120,7 @@
         <v>32</v>
       </c>
       <c r="F191" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G191" t="s">
         <v>14</v>
@@ -7280,7 +7280,7 @@
         <v>27</v>
       </c>
       <c r="F196" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G196" t="s">
         <v>15</v>
@@ -7309,7 +7309,7 @@
         <v>11</v>
       </c>
       <c r="E197" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F197" t="s">
         <v>27</v>
@@ -7533,7 +7533,7 @@
         <v>11</v>
       </c>
       <c r="E204" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F204" t="s">
         <v>23</v>
@@ -7568,7 +7568,7 @@
         <v>23</v>
       </c>
       <c r="F205" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G205" t="s">
         <v>15</v>
@@ -7597,10 +7597,10 @@
         <v>11</v>
       </c>
       <c r="E206" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F206" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G206" t="s">
         <v>14</v>
@@ -7629,10 +7629,10 @@
         <v>11</v>
       </c>
       <c r="E207" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F207" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G207" t="s">
         <v>15</v>
@@ -7664,7 +7664,7 @@
         <v>12</v>
       </c>
       <c r="F208" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G208" t="s">
         <v>15</v>
@@ -7693,7 +7693,7 @@
         <v>11</v>
       </c>
       <c r="E209" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F209" t="s">
         <v>12</v>
@@ -7728,7 +7728,7 @@
         <v>18</v>
       </c>
       <c r="F210" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G210" t="s">
         <v>14</v>
@@ -7757,7 +7757,7 @@
         <v>11</v>
       </c>
       <c r="E211" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F211" t="s">
         <v>18</v>
@@ -7792,7 +7792,7 @@
         <v>13</v>
       </c>
       <c r="F212" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G212" t="s">
         <v>15</v>
@@ -7821,7 +7821,7 @@
         <v>11</v>
       </c>
       <c r="E213" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F213" t="s">
         <v>13</v>
@@ -7856,7 +7856,7 @@
         <v>21</v>
       </c>
       <c r="F214" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G214" t="s">
         <v>14</v>
@@ -7885,7 +7885,7 @@
         <v>11</v>
       </c>
       <c r="E215" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="F215" t="s">
         <v>21</v>
@@ -7917,7 +7917,7 @@
         <v>11</v>
       </c>
       <c r="E216" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F216" t="s">
         <v>32</v>
@@ -7952,7 +7952,7 @@
         <v>32</v>
       </c>
       <c r="F217" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G217" t="s">
         <v>15</v>
@@ -7981,7 +7981,7 @@
         <v>11</v>
       </c>
       <c r="E218" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F218" t="s">
         <v>25</v>
@@ -8016,7 +8016,7 @@
         <v>25</v>
       </c>
       <c r="F219" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G219" t="s">
         <v>15</v>
@@ -8048,7 +8048,7 @@
         <v>19</v>
       </c>
       <c r="F220" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G220" t="s">
         <v>15</v>
@@ -8077,7 +8077,7 @@
         <v>11</v>
       </c>
       <c r="E221" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F221" t="s">
         <v>19</v>
@@ -8173,7 +8173,7 @@
         <v>11</v>
       </c>
       <c r="E224" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F224" t="s">
         <v>13</v>
@@ -8208,7 +8208,7 @@
         <v>13</v>
       </c>
       <c r="F225" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G225" t="s">
         <v>15</v>
@@ -8432,7 +8432,7 @@
         <v>26</v>
       </c>
       <c r="F232" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G232" t="s">
         <v>14</v>
@@ -8461,7 +8461,7 @@
         <v>11</v>
       </c>
       <c r="E233" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F233" t="s">
         <v>26</v>
@@ -8557,7 +8557,7 @@
         <v>11</v>
       </c>
       <c r="E236" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="F236" t="s">
         <v>22</v>
@@ -8592,7 +8592,7 @@
         <v>22</v>
       </c>
       <c r="F237" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G237" t="s">
         <v>15</v>
@@ -8621,7 +8621,7 @@
         <v>11</v>
       </c>
       <c r="E238" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F238" t="s">
         <v>24</v>
@@ -8656,7 +8656,7 @@
         <v>24</v>
       </c>
       <c r="F239" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G239" t="s">
         <v>15</v>
@@ -8688,7 +8688,7 @@
         <v>12</v>
       </c>
       <c r="F240" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G240" t="s">
         <v>15</v>
@@ -8717,7 +8717,7 @@
         <v>11</v>
       </c>
       <c r="E241" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F241" t="s">
         <v>12</v>
@@ -8813,10 +8813,10 @@
         <v>11</v>
       </c>
       <c r="E244" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F244" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G244" t="s">
         <v>14</v>
@@ -8845,10 +8845,10 @@
         <v>11</v>
       </c>
       <c r="E245" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F245" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G245" t="s">
         <v>15</v>
@@ -8941,7 +8941,7 @@
         <v>11</v>
       </c>
       <c r="E248" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F248" t="s">
         <v>28</v>
@@ -8976,7 +8976,7 @@
         <v>28</v>
       </c>
       <c r="F249" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G249" t="s">
         <v>15</v>
@@ -9008,7 +9008,7 @@
         <v>19</v>
       </c>
       <c r="F250" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G250" t="s">
         <v>14</v>
@@ -9037,7 +9037,7 @@
         <v>11</v>
       </c>
       <c r="E251" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F251" t="s">
         <v>19</v>
@@ -9200,7 +9200,7 @@
         <v>27</v>
       </c>
       <c r="F256" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G256" t="s">
         <v>14</v>
@@ -9229,7 +9229,7 @@
         <v>11</v>
       </c>
       <c r="E257" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F257" t="s">
         <v>27</v>
@@ -9261,10 +9261,10 @@
         <v>11</v>
       </c>
       <c r="E258" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="F258" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G258" t="s">
         <v>15</v>
@@ -9293,10 +9293,10 @@
         <v>11</v>
       </c>
       <c r="E259" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F259" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G259" t="s">
         <v>14</v>
@@ -9453,7 +9453,7 @@
         <v>11</v>
       </c>
       <c r="E264" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F264" t="s">
         <v>33</v>
@@ -9488,7 +9488,7 @@
         <v>33</v>
       </c>
       <c r="F265" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G265" t="s">
         <v>14</v>
@@ -9645,7 +9645,7 @@
         <v>11</v>
       </c>
       <c r="E270" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F270" t="s">
         <v>17</v>
@@ -9680,7 +9680,7 @@
         <v>17</v>
       </c>
       <c r="F271" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G271" t="s">
         <v>14</v>
@@ -9709,7 +9709,7 @@
         <v>11</v>
       </c>
       <c r="E272" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F272" t="s">
         <v>34</v>
@@ -9744,7 +9744,7 @@
         <v>34</v>
       </c>
       <c r="F273" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G273" t="s">
         <v>14</v>
@@ -9840,7 +9840,7 @@
         <v>12</v>
       </c>
       <c r="F276" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G276" t="s">
         <v>14</v>
@@ -9869,7 +9869,7 @@
         <v>11</v>
       </c>
       <c r="E277" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F277" t="s">
         <v>12</v>
@@ -10096,7 +10096,7 @@
         <v>18</v>
       </c>
       <c r="F284" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G284" t="s">
         <v>15</v>
@@ -10125,7 +10125,7 @@
         <v>11</v>
       </c>
       <c r="E285" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F285" t="s">
         <v>18</v>
@@ -10157,10 +10157,10 @@
         <v>11</v>
       </c>
       <c r="E286" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F286" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G286" t="s">
         <v>15</v>
@@ -10189,10 +10189,10 @@
         <v>11</v>
       </c>
       <c r="E287" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F287" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G287" t="s">
         <v>14</v>
@@ -10477,7 +10477,7 @@
         <v>11</v>
       </c>
       <c r="E296" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="F296" t="s">
         <v>25</v>
@@ -10512,7 +10512,7 @@
         <v>25</v>
       </c>
       <c r="F297" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G297" t="s">
         <v>15</v>
@@ -10544,7 +10544,7 @@
         <v>16</v>
       </c>
       <c r="F298" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G298" t="s">
         <v>15</v>
@@ -10573,7 +10573,7 @@
         <v>11</v>
       </c>
       <c r="E299" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F299" t="s">
         <v>16</v>
@@ -10608,7 +10608,7 @@
         <v>21</v>
       </c>
       <c r="F300" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G300" t="s">
         <v>14</v>
@@ -10637,7 +10637,7 @@
         <v>11</v>
       </c>
       <c r="E301" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F301" t="s">
         <v>21</v>
@@ -10669,7 +10669,7 @@
         <v>11</v>
       </c>
       <c r="E302" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F302" t="s">
         <v>28</v>
@@ -10704,7 +10704,7 @@
         <v>28</v>
       </c>
       <c r="F303" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G303" t="s">
         <v>14</v>
@@ -10736,7 +10736,7 @@
         <v>30</v>
       </c>
       <c r="F304" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G304" t="s">
         <v>15</v>
@@ -10765,7 +10765,7 @@
         <v>11</v>
       </c>
       <c r="E305" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F305" t="s">
         <v>30</v>
@@ -10800,7 +10800,7 @@
         <v>16</v>
       </c>
       <c r="F306" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G306" t="s">
         <v>14</v>
@@ -10829,7 +10829,7 @@
         <v>11</v>
       </c>
       <c r="E307" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F307" t="s">
         <v>16</v>
@@ -10928,7 +10928,7 @@
         <v>22</v>
       </c>
       <c r="F310" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G310" t="s">
         <v>14</v>
@@ -10957,7 +10957,7 @@
         <v>11</v>
       </c>
       <c r="E311" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F311" t="s">
         <v>22</v>
@@ -10989,7 +10989,7 @@
         <v>11</v>
       </c>
       <c r="E312" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F312" t="s">
         <v>31</v>
@@ -11024,7 +11024,7 @@
         <v>31</v>
       </c>
       <c r="F313" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G313" t="s">
         <v>15</v>
@@ -11056,7 +11056,7 @@
         <v>30</v>
       </c>
       <c r="F314" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G314" t="s">
         <v>14</v>
@@ -11085,7 +11085,7 @@
         <v>11</v>
       </c>
       <c r="E315" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F315" t="s">
         <v>30</v>
@@ -11248,7 +11248,7 @@
         <v>29</v>
       </c>
       <c r="F320" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G320" t="s">
         <v>15</v>
@@ -11277,7 +11277,7 @@
         <v>11</v>
       </c>
       <c r="E321" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F321" t="s">
         <v>29</v>
@@ -11309,7 +11309,7 @@
         <v>11</v>
       </c>
       <c r="E322" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F322" t="s">
         <v>26</v>
@@ -11344,7 +11344,7 @@
         <v>26</v>
       </c>
       <c r="F323" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G323" t="s">
         <v>14</v>
@@ -11376,7 +11376,7 @@
         <v>34</v>
       </c>
       <c r="F324" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G324" t="s">
         <v>15</v>
@@ -11405,7 +11405,7 @@
         <v>11</v>
       </c>
       <c r="E325" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F325" t="s">
         <v>34</v>
@@ -11565,7 +11565,7 @@
         <v>11</v>
       </c>
       <c r="E330" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="F330" t="s">
         <v>27</v>
@@ -11600,7 +11600,7 @@
         <v>27</v>
       </c>
       <c r="F331" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G331" t="s">
         <v>15</v>
@@ -11632,7 +11632,7 @@
         <v>28</v>
       </c>
       <c r="F332" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G332" t="s">
         <v>15</v>
@@ -11661,7 +11661,7 @@
         <v>11</v>
       </c>
       <c r="E333" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F333" t="s">
         <v>28</v>
@@ -11693,7 +11693,7 @@
         <v>11</v>
       </c>
       <c r="E334" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F334" t="s">
         <v>18</v>
@@ -11728,7 +11728,7 @@
         <v>18</v>
       </c>
       <c r="F335" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G335" t="s">
         <v>15</v>
@@ -11885,10 +11885,10 @@
         <v>11</v>
       </c>
       <c r="E340" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F340" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G340" t="s">
         <v>15</v>
@@ -11917,10 +11917,10 @@
         <v>11</v>
       </c>
       <c r="E341" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F341" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G341" t="s">
         <v>14</v>
@@ -12013,7 +12013,7 @@
         <v>11</v>
       </c>
       <c r="E344" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F344" t="s">
         <v>33</v>
@@ -12048,7 +12048,7 @@
         <v>33</v>
       </c>
       <c r="F345" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G345" t="s">
         <v>14</v>
@@ -12077,7 +12077,7 @@
         <v>11</v>
       </c>
       <c r="E346" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F346" t="s">
         <v>29</v>
@@ -12112,7 +12112,7 @@
         <v>29</v>
       </c>
       <c r="F347" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G347" t="s">
         <v>14</v>
@@ -12208,7 +12208,7 @@
         <v>35</v>
       </c>
       <c r="F350" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G350" t="s">
         <v>15</v>
@@ -12237,7 +12237,7 @@
         <v>11</v>
       </c>
       <c r="E351" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F351" t="s">
         <v>35</v>
@@ -12336,7 +12336,7 @@
         <v>17</v>
       </c>
       <c r="F354" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G354" t="s">
         <v>14</v>
@@ -12365,7 +12365,7 @@
         <v>11</v>
       </c>
       <c r="E355" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F355" t="s">
         <v>17</v>
@@ -12400,7 +12400,7 @@
         <v>16</v>
       </c>
       <c r="F356" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G356" t="s">
         <v>15</v>
@@ -12429,7 +12429,7 @@
         <v>11</v>
       </c>
       <c r="E357" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F357" t="s">
         <v>16</v>
@@ -12464,7 +12464,7 @@
         <v>13</v>
       </c>
       <c r="F358" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G358" t="s">
         <v>15</v>
@@ -12493,7 +12493,7 @@
         <v>11</v>
       </c>
       <c r="E359" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="F359" t="s">
         <v>13</v>
@@ -12525,7 +12525,7 @@
         <v>11</v>
       </c>
       <c r="E360" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F360" t="s">
         <v>24</v>
@@ -12560,7 +12560,7 @@
         <v>24</v>
       </c>
       <c r="F361" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G361" t="s">
         <v>15</v>
@@ -12589,7 +12589,7 @@
         <v>11</v>
       </c>
       <c r="E362" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F362" t="s">
         <v>33</v>
@@ -12624,7 +12624,7 @@
         <v>33</v>
       </c>
       <c r="F363" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G363" t="s">
         <v>15</v>
@@ -12720,7 +12720,7 @@
         <v>12</v>
       </c>
       <c r="F366" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G366" t="s">
         <v>14</v>
@@ -12749,7 +12749,7 @@
         <v>11</v>
       </c>
       <c r="E367" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F367" t="s">
         <v>12</v>
@@ -12781,7 +12781,7 @@
         <v>11</v>
       </c>
       <c r="E368" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="F368" t="s">
         <v>19</v>
@@ -12816,7 +12816,7 @@
         <v>19</v>
       </c>
       <c r="F369" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G369" t="s">
         <v>14</v>
@@ -12976,7 +12976,7 @@
         <v>34</v>
       </c>
       <c r="F374" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G374" t="s">
         <v>15</v>
@@ -13005,7 +13005,7 @@
         <v>11</v>
       </c>
       <c r="E375" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F375" t="s">
         <v>34</v>
@@ -13037,7 +13037,7 @@
         <v>11</v>
       </c>
       <c r="E376" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F376" t="s">
         <v>25</v>
@@ -13072,7 +13072,7 @@
         <v>25</v>
       </c>
       <c r="F377" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G377" t="s">
         <v>15</v>
@@ -13229,7 +13229,7 @@
         <v>11</v>
       </c>
       <c r="E382" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F382" t="s">
         <v>23</v>
@@ -13264,7 +13264,7 @@
         <v>23</v>
       </c>
       <c r="F383" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G383" t="s">
         <v>14</v>
@@ -13293,7 +13293,7 @@
         <v>11</v>
       </c>
       <c r="E384" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F384" t="s">
         <v>22</v>
@@ -13328,7 +13328,7 @@
         <v>22</v>
       </c>
       <c r="F385" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G385" t="s">
         <v>14</v>
@@ -13424,7 +13424,7 @@
         <v>20</v>
       </c>
       <c r="F388" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G388" t="s">
         <v>14</v>
@@ -13453,7 +13453,7 @@
         <v>11</v>
       </c>
       <c r="E389" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F389" t="s">
         <v>20</v>
@@ -13488,7 +13488,7 @@
         <v>35</v>
       </c>
       <c r="F390" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G390" t="s">
         <v>14</v>
@@ -13517,7 +13517,7 @@
         <v>11</v>
       </c>
       <c r="E391" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F391" t="s">
         <v>35</v>
@@ -13549,7 +13549,7 @@
         <v>11</v>
       </c>
       <c r="E392" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F392" t="s">
         <v>17</v>
@@ -13584,7 +13584,7 @@
         <v>17</v>
       </c>
       <c r="F393" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G393" t="s">
         <v>15</v>
@@ -13744,7 +13744,7 @@
         <v>18</v>
       </c>
       <c r="F398" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G398" t="s">
         <v>14</v>
@@ -13773,7 +13773,7 @@
         <v>11</v>
       </c>
       <c r="E399" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F399" t="s">
         <v>18</v>
@@ -13872,7 +13872,7 @@
         <v>30</v>
       </c>
       <c r="F402" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G402" t="s">
         <v>14</v>
@@ -13901,7 +13901,7 @@
         <v>11</v>
       </c>
       <c r="E403" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F403" t="s">
         <v>30</v>
@@ -13997,10 +13997,10 @@
         <v>11</v>
       </c>
       <c r="E406" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F406" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G406" t="s">
         <v>14</v>
@@ -14029,10 +14029,10 @@
         <v>11</v>
       </c>
       <c r="E407" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F407" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G407" t="s">
         <v>15</v>
@@ -14125,7 +14125,7 @@
         <v>11</v>
       </c>
       <c r="E410" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F410" t="s">
         <v>20</v>
@@ -14160,7 +14160,7 @@
         <v>20</v>
       </c>
       <c r="F411" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G411" t="s">
         <v>15</v>
@@ -14189,7 +14189,7 @@
         <v>11</v>
       </c>
       <c r="E412" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F412" t="s">
         <v>24</v>
@@ -14224,7 +14224,7 @@
         <v>24</v>
       </c>
       <c r="F413" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G413" t="s">
         <v>15</v>
@@ -14256,7 +14256,7 @@
         <v>12</v>
       </c>
       <c r="F414" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G414" t="s">
         <v>14</v>
@@ -14285,7 +14285,7 @@
         <v>11</v>
       </c>
       <c r="E415" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="F415" t="s">
         <v>12</v>
@@ -14320,7 +14320,7 @@
         <v>27</v>
       </c>
       <c r="F416" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G416" t="s">
         <v>15</v>
@@ -14349,7 +14349,7 @@
         <v>11</v>
       </c>
       <c r="E417" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F417" t="s">
         <v>27</v>
@@ -14381,10 +14381,10 @@
         <v>11</v>
       </c>
       <c r="E418" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F418" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G418" t="s">
         <v>15</v>
@@ -14413,10 +14413,10 @@
         <v>11</v>
       </c>
       <c r="E419" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F419" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G419" t="s">
         <v>14</v>
@@ -14445,7 +14445,7 @@
         <v>11</v>
       </c>
       <c r="E420" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F420" t="s">
         <v>23</v>
@@ -14480,7 +14480,7 @@
         <v>23</v>
       </c>
       <c r="F421" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G421" t="s">
         <v>14</v>
@@ -14576,7 +14576,7 @@
         <v>12</v>
       </c>
       <c r="F424" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G424" t="s">
         <v>15</v>
@@ -14605,7 +14605,7 @@
         <v>11</v>
       </c>
       <c r="E425" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F425" t="s">
         <v>12</v>
@@ -14701,7 +14701,7 @@
         <v>11</v>
       </c>
       <c r="E428" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F428" t="s">
         <v>31</v>
@@ -14736,7 +14736,7 @@
         <v>31</v>
       </c>
       <c r="F429" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G429" t="s">
         <v>14</v>
@@ -14765,7 +14765,7 @@
         <v>11</v>
       </c>
       <c r="E430" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F430" t="s">
         <v>22</v>
@@ -14800,7 +14800,7 @@
         <v>22</v>
       </c>
       <c r="F431" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G431" t="s">
         <v>14</v>
@@ -14896,7 +14896,7 @@
         <v>20</v>
       </c>
       <c r="F434" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G434" t="s">
         <v>15</v>
@@ -14925,7 +14925,7 @@
         <v>11</v>
       </c>
       <c r="E435" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F435" t="s">
         <v>20</v>
@@ -15149,10 +15149,10 @@
         <v>11</v>
       </c>
       <c r="E442" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F442" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G442" t="s">
         <v>15</v>
@@ -15181,10 +15181,10 @@
         <v>11</v>
       </c>
       <c r="E443" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="F443" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G443" t="s">
         <v>14</v>
@@ -15344,7 +15344,7 @@
         <v>19</v>
       </c>
       <c r="F448" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G448" t="s">
         <v>15</v>
@@ -15373,7 +15373,7 @@
         <v>11</v>
       </c>
       <c r="E449" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F449" t="s">
         <v>19</v>
@@ -15405,7 +15405,7 @@
         <v>11</v>
       </c>
       <c r="E450" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="F450" t="s">
         <v>35</v>
@@ -15440,7 +15440,7 @@
         <v>35</v>
       </c>
       <c r="F451" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G451" t="s">
         <v>15</v>
@@ -15725,7 +15725,7 @@
         <v>11</v>
       </c>
       <c r="E460" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F460" t="s">
         <v>24</v>
@@ -15760,7 +15760,7 @@
         <v>24</v>
       </c>
       <c r="F461" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G461" t="s">
         <v>14</v>
@@ -15792,7 +15792,7 @@
         <v>27</v>
       </c>
       <c r="F462" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G462" t="s">
         <v>14</v>
@@ -15821,7 +15821,7 @@
         <v>11</v>
       </c>
       <c r="E463" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F463" t="s">
         <v>27</v>
@@ -15917,10 +15917,10 @@
         <v>11</v>
       </c>
       <c r="E466" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F466" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G466" t="s">
         <v>15</v>
@@ -15949,10 +15949,10 @@
         <v>11</v>
       </c>
       <c r="E467" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F467" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G467" t="s">
         <v>14</v>
@@ -15981,7 +15981,7 @@
         <v>11</v>
       </c>
       <c r="E468" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F468" t="s">
         <v>16</v>
@@ -16016,7 +16016,7 @@
         <v>16</v>
       </c>
       <c r="F469" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G469" t="s">
         <v>15</v>
@@ -16173,7 +16173,7 @@
         <v>11</v>
       </c>
       <c r="E474" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F474" t="s">
         <v>31</v>
@@ -16208,7 +16208,7 @@
         <v>31</v>
       </c>
       <c r="F475" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G475" t="s">
         <v>15</v>
@@ -16240,7 +16240,7 @@
         <v>30</v>
       </c>
       <c r="F476" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G476" t="s">
         <v>14</v>
@@ -16269,7 +16269,7 @@
         <v>11</v>
       </c>
       <c r="E477" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F477" t="s">
         <v>30</v>
@@ -16301,10 +16301,10 @@
         <v>11</v>
       </c>
       <c r="E478" t="s">
+        <v>36</v>
+      </c>
+      <c r="F478" t="s">
         <v>38</v>
-      </c>
-      <c r="F478" t="s">
-        <v>40</v>
       </c>
       <c r="G478" t="s">
         <v>14</v>
@@ -16333,10 +16333,10 @@
         <v>11</v>
       </c>
       <c r="E479" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F479" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G479" t="s">
         <v>15</v>
@@ -16621,7 +16621,7 @@
         <v>11</v>
       </c>
       <c r="E488" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="F488" t="s">
         <v>26</v>
@@ -16656,7 +16656,7 @@
         <v>26</v>
       </c>
       <c r="F489" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G489" t="s">
         <v>14</v>
@@ -16749,7 +16749,7 @@
         <v>11</v>
       </c>
       <c r="E492" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F492" t="s">
         <v>21</v>
@@ -16784,7 +16784,7 @@
         <v>21</v>
       </c>
       <c r="F493" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G493" t="s">
         <v>15</v>
@@ -16816,7 +16816,7 @@
         <v>20</v>
       </c>
       <c r="F494" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G494" t="s">
         <v>14</v>
@@ -16845,7 +16845,7 @@
         <v>11</v>
       </c>
       <c r="E495" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F495" t="s">
         <v>20</v>
@@ -16877,7 +16877,7 @@
         <v>11</v>
       </c>
       <c r="E496" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F496" t="s">
         <v>23</v>
@@ -16912,7 +16912,7 @@
         <v>23</v>
       </c>
       <c r="F497" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G497" t="s">
         <v>15</v>
@@ -17008,7 +17008,7 @@
         <v>16</v>
       </c>
       <c r="F500" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G500" t="s">
         <v>14</v>
@@ -17037,7 +17037,7 @@
         <v>11</v>
       </c>
       <c r="E501" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F501" t="s">
         <v>16</v>
@@ -17133,7 +17133,7 @@
         <v>11</v>
       </c>
       <c r="E504" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F504" t="s">
         <v>22</v>
@@ -17168,7 +17168,7 @@
         <v>22</v>
       </c>
       <c r="F505" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G505" t="s">
         <v>14</v>
@@ -17200,7 +17200,7 @@
         <v>30</v>
       </c>
       <c r="F506" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G506" t="s">
         <v>15</v>
@@ -17229,7 +17229,7 @@
         <v>11</v>
       </c>
       <c r="E507" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F507" t="s">
         <v>30</v>
@@ -17325,7 +17325,7 @@
         <v>11</v>
       </c>
       <c r="E510" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F510" t="s">
         <v>19</v>
@@ -17360,7 +17360,7 @@
         <v>19</v>
       </c>
       <c r="F511" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G511" t="s">
         <v>15</v>
@@ -17389,10 +17389,10 @@
         <v>11</v>
       </c>
       <c r="E512" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F512" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G512" t="s">
         <v>15</v>
@@ -17421,10 +17421,10 @@
         <v>11</v>
       </c>
       <c r="E513" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F513" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G513" t="s">
         <v>14</v>
@@ -17456,7 +17456,7 @@
         <v>13</v>
       </c>
       <c r="F514" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G514" t="s">
         <v>14</v>
@@ -17485,7 +17485,7 @@
         <v>11</v>
       </c>
       <c r="E515" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F515" t="s">
         <v>13</v>
@@ -17837,10 +17837,10 @@
         <v>11</v>
       </c>
       <c r="E526" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F526" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G526" t="s">
         <v>15</v>
@@ -17869,10 +17869,10 @@
         <v>11</v>
       </c>
       <c r="E527" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F527" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G527" t="s">
         <v>14</v>
@@ -17965,7 +17965,7 @@
         <v>11</v>
       </c>
       <c r="E530" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F530" t="s">
         <v>22</v>
@@ -18000,7 +18000,7 @@
         <v>22</v>
       </c>
       <c r="F531" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G531" t="s">
         <v>15</v>
@@ -18096,7 +18096,7 @@
         <v>21</v>
       </c>
       <c r="F534" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G534" t="s">
         <v>14</v>
@@ -18125,7 +18125,7 @@
         <v>11</v>
       </c>
       <c r="E535" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F535" t="s">
         <v>21</v>
@@ -18221,7 +18221,7 @@
         <v>11</v>
       </c>
       <c r="E538" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F538" t="s">
         <v>30</v>
@@ -18256,7 +18256,7 @@
         <v>30</v>
       </c>
       <c r="F539" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G539" t="s">
         <v>15</v>
@@ -18285,10 +18285,10 @@
         <v>11</v>
       </c>
       <c r="E540" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="F540" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G540" t="s">
         <v>15</v>
@@ -18317,10 +18317,10 @@
         <v>11</v>
       </c>
       <c r="E541" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F541" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G541" t="s">
         <v>14</v>
@@ -18352,7 +18352,7 @@
         <v>34</v>
       </c>
       <c r="F542" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G542" t="s">
         <v>15</v>
@@ -18381,7 +18381,7 @@
         <v>11</v>
       </c>
       <c r="E543" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F543" t="s">
         <v>34</v>
@@ -18413,7 +18413,7 @@
         <v>11</v>
       </c>
       <c r="E544" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F544" t="s">
         <v>32</v>
@@ -18448,7 +18448,7 @@
         <v>32</v>
       </c>
       <c r="F545" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G545" t="s">
         <v>15</v>
@@ -18471,16 +18471,16 @@
         <v>2024</v>
       </c>
       <c r="C546" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D546" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E546" t="s">
         <v>28</v>
       </c>
       <c r="F546" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G546" t="s">
         <v>14</v>
@@ -18503,13 +18503,13 @@
         <v>2024</v>
       </c>
       <c r="C547" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D547" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E547" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="F547" t="s">
         <v>28</v>
@@ -18535,10 +18535,10 @@
         <v>2024</v>
       </c>
       <c r="C548" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D548" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E548" t="s">
         <v>13</v>
@@ -18567,10 +18567,10 @@
         <v>2024</v>
       </c>
       <c r="C549" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D549" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E549" t="s">
         <v>18</v>
@@ -18599,10 +18599,10 @@
         <v>2024</v>
       </c>
       <c r="C550" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D550" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E550" t="s">
         <v>20</v>
@@ -18631,10 +18631,10 @@
         <v>2024</v>
       </c>
       <c r="C551" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D551" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E551" t="s">
         <v>35</v>
@@ -18663,10 +18663,10 @@
         <v>2024</v>
       </c>
       <c r="C552" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D552" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E552" t="s">
         <v>16</v>
@@ -18695,10 +18695,10 @@
         <v>2024</v>
       </c>
       <c r="C553" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D553" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E553" t="s">
         <v>17</v>
@@ -18727,16 +18727,16 @@
         <v>2024</v>
       </c>
       <c r="C554" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D554" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E554" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F554" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G554" t="s">
         <v>15</v>
@@ -18759,16 +18759,16 @@
         <v>2024</v>
       </c>
       <c r="C555" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D555" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E555" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F555" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G555" t="s">
         <v>14</v>
@@ -18791,13 +18791,13 @@
         <v>2024</v>
       </c>
       <c r="C556" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D556" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E556" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F556" t="s">
         <v>32</v>
@@ -18823,16 +18823,16 @@
         <v>2024</v>
       </c>
       <c r="C557" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D557" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E557" t="s">
         <v>32</v>
       </c>
       <c r="F557" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G557" t="s">
         <v>15</v>
@@ -18855,10 +18855,10 @@
         <v>2024</v>
       </c>
       <c r="C558" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D558" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E558" t="s">
         <v>12</v>
@@ -18887,10 +18887,10 @@
         <v>2024</v>
       </c>
       <c r="C559" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D559" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E559" t="s">
         <v>28</v>
@@ -18919,16 +18919,16 @@
         <v>2024</v>
       </c>
       <c r="C560" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D560" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E560" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F560" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G560" t="s">
         <v>15</v>
@@ -18951,16 +18951,16 @@
         <v>2024</v>
       </c>
       <c r="C561" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D561" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E561" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F561" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G561" t="s">
         <v>14</v>
@@ -18983,16 +18983,16 @@
         <v>2024</v>
       </c>
       <c r="C562" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D562" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E562" t="s">
         <v>16</v>
       </c>
       <c r="F562" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G562" t="s">
         <v>14</v>
@@ -19015,13 +19015,13 @@
         <v>2024</v>
       </c>
       <c r="C563" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D563" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E563" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F563" t="s">
         <v>16</v>
@@ -19047,10 +19047,10 @@
         <v>2024</v>
       </c>
       <c r="C564" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D564" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E564" t="s">
         <v>20</v>
@@ -19079,10 +19079,10 @@
         <v>2024</v>
       </c>
       <c r="C565" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D565" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E565" t="s">
         <v>13</v>
@@ -19111,16 +19111,16 @@
         <v>2024</v>
       </c>
       <c r="C566" t="s">
+        <v>43</v>
+      </c>
+      <c r="D566" t="s">
         <v>46</v>
-      </c>
-      <c r="D566" t="s">
-        <v>49</v>
       </c>
       <c r="E566" t="s">
         <v>16</v>
       </c>
       <c r="F566" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G566" t="s">
         <v>14</v>
@@ -19143,13 +19143,13 @@
         <v>2024</v>
       </c>
       <c r="C567" t="s">
+        <v>43</v>
+      </c>
+      <c r="D567" t="s">
         <v>46</v>
       </c>
-      <c r="D567" t="s">
-        <v>49</v>
-      </c>
       <c r="E567" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F567" t="s">
         <v>16</v>
@@ -19175,10 +19175,10 @@
         <v>2024</v>
       </c>
       <c r="C568" t="s">
+        <v>43</v>
+      </c>
+      <c r="D568" t="s">
         <v>46</v>
-      </c>
-      <c r="D568" t="s">
-        <v>49</v>
       </c>
       <c r="E568" t="s">
         <v>12</v>
@@ -19207,10 +19207,10 @@
         <v>2024</v>
       </c>
       <c r="C569" t="s">
+        <v>43</v>
+      </c>
+      <c r="D569" t="s">
         <v>46</v>
-      </c>
-      <c r="D569" t="s">
-        <v>49</v>
       </c>
       <c r="E569" t="s">
         <v>20</v>
@@ -19239,10 +19239,10 @@
         <v>2024</v>
       </c>
       <c r="C570" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D570" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E570" t="s">
         <v>16</v>
@@ -19251,7 +19251,7 @@
         <v>12</v>
       </c>
       <c r="G570" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H570">
         <v>40</v>
@@ -19271,10 +19271,10 @@
         <v>2024</v>
       </c>
       <c r="C571" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D571" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E571" t="s">
         <v>12</v>
@@ -19283,7 +19283,7 @@
         <v>16</v>
       </c>
       <c r="G571" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H571">
         <v>22</v>
